--- a/data/commodity/Lumber Futures.xlsx
+++ b/data/commodity/Lumber Futures.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/commodity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC07B5E-E1D8-4C42-88AD-45AB0693ADE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182F71AB-88BF-1B46-8554-BE6A378F990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="12120" xr2:uid="{992386F8-3C03-4FEC-9C85-F1F4A57F5E1F}"/>
+    <workbookView xWindow="8980" yWindow="3340" windowWidth="28800" windowHeight="12120" xr2:uid="{992386F8-3C03-4FEC-9C85-F1F4A57F5E1F}"/>
   </bookViews>
   <sheets>
     <sheet name="lumber" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1670301-04F7-4CBF-B9A8-B7E6613CDDDD}">
-  <dimension ref="A1:B11655"/>
+  <dimension ref="A1:B11656"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" bestFit="1" customWidth="1"/>
@@ -93702,6 +93702,14 @@
       </c>
       <c r="B11655" s="1">
         <v>550.5</v>
+      </c>
+    </row>
+    <row r="11656" spans="1:2">
+      <c r="A11656" s="2">
+        <v>46017</v>
+      </c>
+      <c r="B11656" s="1">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
